--- a/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486941_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486941_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.2936</v>
+        <v>5.782</v>
       </c>
       <c r="E2" t="n">
-        <v>4.7104</v>
+        <v>4.1099</v>
       </c>
       <c r="F2" t="n">
-        <v>1.5831</v>
+        <v>1.6721</v>
       </c>
       <c r="G2" t="n">
         <v>3.0445</v>
@@ -610,13 +610,13 @@
         <v>1.6427</v>
       </c>
       <c r="S2" t="n">
-        <v>0.5590000000000001</v>
+        <v>0.0475</v>
       </c>
       <c r="T2" t="n">
-        <v>0.4066</v>
+        <v>-0.1939</v>
       </c>
       <c r="U2" t="n">
-        <v>0.1524</v>
+        <v>0.2413</v>
       </c>
       <c r="V2" t="n">
         <v>1.0472</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>N. ZIZIC</t>
+          <t>E. STOILOV</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,64 +643,64 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.5552</v>
+        <v>4.119</v>
       </c>
       <c r="E3" t="n">
-        <v>4.658</v>
+        <v>3.094</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.1029</v>
+        <v>1.0249</v>
       </c>
       <c r="G3" t="n">
-        <v>2.7156</v>
+        <v>2.8666</v>
       </c>
       <c r="H3" t="n">
-        <v>3.1892</v>
+        <v>1.2167</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.4736</v>
+        <v>1.6499</v>
       </c>
       <c r="J3" t="n">
-        <v>4.0882</v>
+        <v>3.0576</v>
       </c>
       <c r="K3" t="n">
-        <v>4.0752</v>
+        <v>2.2683</v>
       </c>
       <c r="L3" t="n">
-        <v>0.013</v>
+        <v>0.7893</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.3726</v>
+        <v>-0.191</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.886</v>
+        <v>-1.0516</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.4866</v>
+        <v>0.8606</v>
       </c>
       <c r="P3" t="n">
-        <v>1.4374</v>
+        <v>-0.4107</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>-2.0534</v>
       </c>
       <c r="R3" t="n">
-        <v>1.4374</v>
+        <v>1.6427</v>
       </c>
       <c r="S3" t="n">
-        <v>0.9915</v>
+        <v>0.2442</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.0195</v>
+        <v>-0.5077</v>
       </c>
       <c r="U3" t="n">
-        <v>1.011</v>
+        <v>0.7518</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.5893</v>
+        <v>1.4189</v>
       </c>
       <c r="W3" t="n">
-        <v>0.5893</v>
+        <v>2.5975</v>
       </c>
       <c r="X3" t="n">
         <v>-1.1786</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>E. STOILOV</t>
+          <t>N. ZIZIC</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,64 +721,64 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>4.305</v>
+        <v>4.0858</v>
       </c>
       <c r="E4" t="n">
-        <v>2.6872</v>
+        <v>4.5147</v>
       </c>
       <c r="F4" t="n">
-        <v>1.6178</v>
+        <v>-0.4289</v>
       </c>
       <c r="G4" t="n">
-        <v>2.8666</v>
+        <v>2.7156</v>
       </c>
       <c r="H4" t="n">
-        <v>1.2167</v>
+        <v>3.1892</v>
       </c>
       <c r="I4" t="n">
-        <v>1.6499</v>
+        <v>-0.4736</v>
       </c>
       <c r="J4" t="n">
-        <v>3.0576</v>
+        <v>4.0882</v>
       </c>
       <c r="K4" t="n">
-        <v>2.2683</v>
+        <v>4.0752</v>
       </c>
       <c r="L4" t="n">
-        <v>0.7893</v>
+        <v>0.013</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.191</v>
+        <v>-1.3726</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.0516</v>
+        <v>-0.886</v>
       </c>
       <c r="O4" t="n">
-        <v>0.8606</v>
+        <v>-0.4866</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.4107</v>
+        <v>1.4374</v>
       </c>
       <c r="Q4" t="n">
-        <v>-2.0534</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1.6427</v>
+        <v>1.4374</v>
       </c>
       <c r="S4" t="n">
-        <v>0.4302</v>
+        <v>0.5221</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.9145</v>
+        <v>-0.1628</v>
       </c>
       <c r="U4" t="n">
-        <v>1.3447</v>
+        <v>0.6849</v>
       </c>
       <c r="V4" t="n">
-        <v>1.4189</v>
+        <v>-0.5893</v>
       </c>
       <c r="W4" t="n">
-        <v>2.5975</v>
+        <v>0.5893</v>
       </c>
       <c r="X4" t="n">
         <v>-1.1786</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>3.2418</v>
+        <v>3.6643</v>
       </c>
       <c r="E5" t="n">
-        <v>3.4107</v>
+        <v>3.9221</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.1689</v>
+        <v>-0.2578</v>
       </c>
       <c r="G5" t="n">
         <v>1.6265</v>
@@ -844,13 +844,13 @@
         <v>1.8481</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.6249</v>
+        <v>-0.2024</v>
       </c>
       <c r="T5" t="n">
-        <v>-1.178</v>
+        <v>-0.6665</v>
       </c>
       <c r="U5" t="n">
-        <v>0.5531</v>
+        <v>0.4641</v>
       </c>
       <c r="V5" t="n">
         <v>1.4189</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>2.2027</v>
+        <v>2.8286</v>
       </c>
       <c r="E6" t="n">
-        <v>1.2406</v>
+        <v>1.659</v>
       </c>
       <c r="F6" t="n">
-        <v>0.9621</v>
+        <v>1.1696</v>
       </c>
       <c r="G6" t="n">
         <v>-0.0454</v>
@@ -922,13 +922,13 @@
         <v>1.2321</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.9038</v>
+        <v>-0.2779</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.7169</v>
+        <v>-0.2985</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.187</v>
+        <v>0.0205</v>
       </c>
       <c r="V6" t="n">
         <v>2.9466</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>R. GOMEZ BARRAL</t>
+          <t>G. BLAT BAEZA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.0633</v>
+        <v>0.0148</v>
       </c>
       <c r="E7" t="n">
-        <v>0.5731000000000001</v>
+        <v>1.8249</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.6365</v>
+        <v>-1.8101</v>
       </c>
       <c r="G7" t="n">
-        <v>0.299</v>
+        <v>1.3759</v>
       </c>
       <c r="H7" t="n">
-        <v>0.7461</v>
+        <v>0.4896</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.4472</v>
+        <v>0.8863</v>
       </c>
       <c r="J7" t="n">
-        <v>1.5612</v>
+        <v>1.983</v>
       </c>
       <c r="K7" t="n">
-        <v>1.5217</v>
+        <v>1.6546</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0395</v>
+        <v>0.3284</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.2623</v>
+        <v>-0.6071</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.7756</v>
+        <v>-1.1649</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.4866</v>
+        <v>0.5579</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.4107</v>
+        <v>0.2053</v>
       </c>
       <c r="Q7" t="n">
         <v>-1.0267</v>
       </c>
       <c r="R7" t="n">
-        <v>0.616</v>
+        <v>1.2321</v>
       </c>
       <c r="S7" t="n">
-        <v>0.0484</v>
+        <v>0.2015</v>
       </c>
       <c r="T7" t="n">
-        <v>0.0386</v>
+        <v>-0.31</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0098</v>
+        <v>0.5115</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>-1.7679</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.1786</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-2.9466</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>G. BLAT BAEZA</t>
+          <t>R. GOMEZ BARRAL</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.1417</v>
+        <v>-0.2289</v>
       </c>
       <c r="E8" t="n">
-        <v>1.5498</v>
+        <v>0.2593</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.6915</v>
+        <v>-0.4883</v>
       </c>
       <c r="G8" t="n">
-        <v>1.3759</v>
+        <v>0.299</v>
       </c>
       <c r="H8" t="n">
-        <v>0.4896</v>
+        <v>0.7461</v>
       </c>
       <c r="I8" t="n">
-        <v>0.8863</v>
+        <v>-0.4472</v>
       </c>
       <c r="J8" t="n">
-        <v>1.983</v>
+        <v>1.5612</v>
       </c>
       <c r="K8" t="n">
-        <v>1.6546</v>
+        <v>1.5217</v>
       </c>
       <c r="L8" t="n">
-        <v>0.3284</v>
+        <v>0.0395</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.6071</v>
+        <v>-1.2623</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.1649</v>
+        <v>-0.7756</v>
       </c>
       <c r="O8" t="n">
-        <v>0.5579</v>
+        <v>-0.4866</v>
       </c>
       <c r="P8" t="n">
-        <v>0.2053</v>
+        <v>-0.4107</v>
       </c>
       <c r="Q8" t="n">
         <v>-1.0267</v>
       </c>
       <c r="R8" t="n">
-        <v>1.2321</v>
+        <v>0.616</v>
       </c>
       <c r="S8" t="n">
-        <v>0.045</v>
+        <v>-0.1172</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.5851</v>
+        <v>-0.2752</v>
       </c>
       <c r="U8" t="n">
-        <v>0.6301</v>
+        <v>0.158</v>
       </c>
       <c r="V8" t="n">
-        <v>-1.7679</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>1.1786</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-2.9466</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.9728</v>
+        <v>-1.529</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.2537</v>
+        <v>-1.0174</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.7191</v>
+        <v>-0.5116000000000001</v>
       </c>
       <c r="G9" t="n">
         <v>-1.8549</v>
@@ -1156,13 +1156,13 @@
         <v>1.2321</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.5204</v>
+        <v>-0.0765</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.6587</v>
+        <v>-0.4224</v>
       </c>
       <c r="U9" t="n">
-        <v>0.1383</v>
+        <v>0.3458</v>
       </c>
       <c r="V9" t="n">
         <v>-0.8295</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.3287</v>
+        <v>-2.4152</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.6428</v>
+        <v>-2.759</v>
       </c>
       <c r="F10" t="n">
-        <v>0.3142</v>
+        <v>0.3438</v>
       </c>
       <c r="G10" t="n">
         <v>-3.3093</v>
@@ -1234,13 +1234,13 @@
         <v>0.8214</v>
       </c>
       <c r="S10" t="n">
-        <v>0.1592</v>
+        <v>0.0727</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.0931</v>
+        <v>-0.2093</v>
       </c>
       <c r="U10" t="n">
-        <v>0.2523</v>
+        <v>0.282</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.6921</v>
+        <v>-2.9337</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.9851</v>
+        <v>-3.6712</v>
       </c>
       <c r="F11" t="n">
-        <v>0.2929</v>
+        <v>0.7376</v>
       </c>
       <c r="G11" t="n">
         <v>-2.4693</v>
@@ -1312,13 +1312,13 @@
         <v>1.6427</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.2495</v>
+        <v>-0.4911</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.9881</v>
+        <v>-0.6743</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.2615</v>
+        <v>0.1832</v>
       </c>
       <c r="V11" t="n">
         <v>-0.5893</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>12.3997</v>
+        <v>13.3877</v>
       </c>
       <c r="E12" t="n">
-        <v>10.9482</v>
+        <v>11.9363</v>
       </c>
       <c r="F12" t="n">
-        <v>1.4512</v>
+        <v>1.4513</v>
       </c>
       <c r="G12" t="n">
         <v>4.249199999999998</v>
@@ -1369,19 +1369,19 @@
         <v>13.7415</v>
       </c>
       <c r="L12" t="n">
-        <v>-2.226099999999999</v>
+        <v>-2.2261</v>
       </c>
       <c r="M12" t="n">
         <v>-7.266299999999999</v>
       </c>
       <c r="N12" t="n">
-        <v>-9.135900000000001</v>
+        <v>-9.135899999999999</v>
       </c>
       <c r="O12" t="n">
         <v>1.8698</v>
       </c>
       <c r="P12" t="n">
-        <v>6.160199999999999</v>
+        <v>6.1602</v>
       </c>
       <c r="Q12" t="n">
         <v>-7.1869</v>
@@ -1390,13 +1390,13 @@
         <v>13.3473</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.0653</v>
+        <v>-0.0771</v>
       </c>
       <c r="T12" t="n">
-        <v>-4.708699999999999</v>
+        <v>-3.7206</v>
       </c>
       <c r="U12" t="n">
-        <v>3.6432</v>
+        <v>3.6431</v>
       </c>
       <c r="V12" t="n">
         <v>3.0556</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>3.7695</v>
+        <v>4.0885</v>
       </c>
       <c r="E13" t="n">
-        <v>4.1756</v>
+        <v>4.3848</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.4061</v>
+        <v>-0.2962</v>
       </c>
       <c r="G13" t="n">
         <v>1.5133</v>
@@ -1468,13 +1468,13 @@
         <v>0.8214</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.7171</v>
+        <v>-0.3981</v>
       </c>
       <c r="T13" t="n">
-        <v>-1.1857</v>
+        <v>-0.9765</v>
       </c>
       <c r="U13" t="n">
-        <v>0.4686</v>
+        <v>0.5784</v>
       </c>
       <c r="V13" t="n">
         <v>2.3573</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>1.1043</v>
+        <v>0.304</v>
       </c>
       <c r="E14" t="n">
-        <v>0.3856</v>
+        <v>-0.3466</v>
       </c>
       <c r="F14" t="n">
-        <v>0.7187</v>
+        <v>0.6506</v>
       </c>
       <c r="G14" t="n">
         <v>-1.0108</v>
@@ -1546,13 +1546,13 @@
         <v>1.4374</v>
       </c>
       <c r="S14" t="n">
-        <v>1.454</v>
+        <v>0.6536999999999999</v>
       </c>
       <c r="T14" t="n">
-        <v>0.577</v>
+        <v>-0.1552</v>
       </c>
       <c r="U14" t="n">
-        <v>0.877</v>
+        <v>0.8090000000000001</v>
       </c>
       <c r="V14" t="n">
         <v>3.5359</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.0989</v>
+        <v>-0.5837</v>
       </c>
       <c r="E15" t="n">
-        <v>0.4162</v>
+        <v>0.207</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.5151</v>
+        <v>-0.7907</v>
       </c>
       <c r="G15" t="n">
         <v>-0.2168</v>
@@ -1624,13 +1624,13 @@
         <v>0.8214</v>
       </c>
       <c r="S15" t="n">
-        <v>1.2616</v>
+        <v>0.7768</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.2907</v>
+        <v>-0.4999</v>
       </c>
       <c r="U15" t="n">
-        <v>1.5523</v>
+        <v>1.2768</v>
       </c>
       <c r="V15" t="n">
         <v>-0.9384</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-1.2409</v>
+        <v>-0.8381999999999999</v>
       </c>
       <c r="E16" t="n">
-        <v>0.7063</v>
+        <v>1.0201</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.9472</v>
+        <v>-1.8583</v>
       </c>
       <c r="G16" t="n">
         <v>0.6262</v>
@@ -1702,13 +1702,13 @@
         <v>0.4107</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.8938</v>
+        <v>-0.4911</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.527</v>
+        <v>-0.2132</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.3669</v>
+        <v>-0.2779</v>
       </c>
       <c r="V16" t="n">
         <v>-1.1786</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-1.6639</v>
+        <v>-1.5</v>
       </c>
       <c r="E17" t="n">
-        <v>-1.1913</v>
+        <v>-1.0867</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.4726</v>
+        <v>-0.4133</v>
       </c>
       <c r="G17" t="n">
         <v>0.0052</v>
@@ -1780,13 +1780,13 @@
         <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.6424</v>
+        <v>-0.4785</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.5928</v>
+        <v>-0.4882</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.0495</v>
+        <v>0.0098</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-2.328</v>
+        <v>-2.1762</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.3575</v>
+        <v>-0.6714</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.9704</v>
+        <v>-1.5049</v>
       </c>
       <c r="G18" t="n">
         <v>1.0817</v>
@@ -1858,13 +1858,13 @@
         <v>1.4374</v>
       </c>
       <c r="S18" t="n">
-        <v>0.535</v>
+        <v>0.6867</v>
       </c>
       <c r="T18" t="n">
-        <v>0.209</v>
+        <v>-0.1048</v>
       </c>
       <c r="U18" t="n">
-        <v>0.3259</v>
+        <v>0.7915</v>
       </c>
       <c r="V18" t="n">
         <v>-1.0698</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-2.5566</v>
+        <v>-2.2968</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.7786</v>
+        <v>-0.5694</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.778</v>
+        <v>-1.7274</v>
       </c>
       <c r="G19" t="n">
         <v>-0.1056</v>
@@ -1936,13 +1936,13 @@
         <v>0.4107</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.067</v>
+        <v>0.1927</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.5928</v>
+        <v>-0.3836</v>
       </c>
       <c r="U19" t="n">
-        <v>0.5258</v>
+        <v>0.5764</v>
       </c>
       <c r="V19" t="n">
         <v>-1.7679</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.9239</v>
+        <v>-2.8384</v>
       </c>
       <c r="E20" t="n">
-        <v>0.3377</v>
+        <v>-0.0808</v>
       </c>
       <c r="F20" t="n">
-        <v>-3.2616</v>
+        <v>-2.7577</v>
       </c>
       <c r="G20" t="n">
         <v>-2.1043</v>
@@ -2014,13 +2014,13 @@
         <v>0.616</v>
       </c>
       <c r="S20" t="n">
-        <v>0.5295</v>
+        <v>0.615</v>
       </c>
       <c r="T20" t="n">
-        <v>0.3408</v>
+        <v>-0.07770000000000001</v>
       </c>
       <c r="U20" t="n">
-        <v>0.1887</v>
+        <v>0.6927</v>
       </c>
       <c r="V20" t="n">
         <v>-0.9384</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-6.4611</v>
+        <v>-5.8614</v>
       </c>
       <c r="E21" t="n">
-        <v>-5.1452</v>
+        <v>-4.3084</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.3159</v>
+        <v>-1.5531</v>
       </c>
       <c r="G21" t="n">
         <v>-4.0381</v>
@@ -2092,13 +2092,13 @@
         <v>1.2321</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.3943</v>
+        <v>0.2053</v>
       </c>
       <c r="T21" t="n">
-        <v>-1.5809</v>
+        <v>-0.7441</v>
       </c>
       <c r="U21" t="n">
-        <v>1.1866</v>
+        <v>0.9494</v>
       </c>
       <c r="V21" t="n">
         <v>-3.0554</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-12.3995</v>
+        <v>-11.7022</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.4512</v>
+        <v>-1.4514</v>
       </c>
       <c r="F22" t="n">
-        <v>-10.9482</v>
+        <v>-10.251</v>
       </c>
       <c r="G22" t="n">
         <v>-4.249199999999999</v>
@@ -2170,13 +2170,13 @@
         <v>7.1871</v>
       </c>
       <c r="S22" t="n">
-        <v>1.0655</v>
+        <v>1.7625</v>
       </c>
       <c r="T22" t="n">
-        <v>-3.6431</v>
+        <v>-3.6432</v>
       </c>
       <c r="U22" t="n">
-        <v>4.708500000000001</v>
+        <v>5.406099999999999</v>
       </c>
       <c r="V22" t="n">
         <v>-3.0553</v>
